--- a/Results/glm_sensitivity_andalucia_excel.xlsx
+++ b/Results/glm_sensitivity_andalucia_excel.xlsx
@@ -1,21 +1,74 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\OneDrive\Desktop\Artigos_coauthor\Iberian_plants\Extinction_dynamics_Iberic\Results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAD6F78-DADA-4218-8B42-8BEC6DBCF3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
+  <si>
+    <t>term</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>mean_estimate</t>
+  </si>
+  <si>
+    <t>sd_estimate</t>
+  </si>
+  <si>
+    <t>median_estimate</t>
+  </si>
+  <si>
+    <t>mean_p</t>
+  </si>
+  <si>
+    <t>prop_significant</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Corrected age</t>
+  </si>
+  <si>
+    <t>Diversification rates</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="173" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -52,24 +105,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +169,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +203,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +238,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,287 +414,245 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>mean_estimate</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sd_estimate</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>median_estimate</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>mean_p</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>prop_significant</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C2">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
         <v>-1.94832389547772</v>
       </c>
-      <c r="D2">
-        <v>0.02662397440765663</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="2">
+        <v>2.6623974407656629E-2</v>
+      </c>
+      <c r="E2" s="2">
         <v>-1.948117321180503</v>
       </c>
-      <c r="F2">
-        <v>5.010793211615325E-54</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="2">
+        <v>5.0107932116153247E-54</v>
+      </c>
+      <c r="G2" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="C3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.277164432737926E-2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1.0033695197456201E-3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1.274777242151743E-2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1.7136511431178059E-2</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>-0.1375512185773598</v>
+      </c>
+      <c r="D4" s="2">
+        <v>6.831350201516094E-2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>-0.13509472627619029</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.75512857311784776</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2">
         <v>-2.047784223857009</v>
       </c>
-      <c r="D3">
-        <v>0.03415009359851726</v>
-      </c>
-      <c r="E3">
-        <v>-2.048660425241098</v>
-      </c>
-      <c r="F3">
+      <c r="D5" s="2">
+        <v>3.4150093598517263E-2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-2.0486604252410978</v>
+      </c>
+      <c r="F5" s="2">
         <v>2.649314052597902E-37</v>
       </c>
-      <c r="G3">
+      <c r="G5" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2.6989921610293031E-2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.1874056964852851E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2.6937864684089461E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1.972493455119969E-2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1.102855904136375E-2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>6.7007464981060263E-2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2.0674468783781139E-2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.90260866950199159</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2">
         <v>-2.172599295368034</v>
       </c>
-      <c r="D4">
-        <v>0.04352437959694554</v>
-      </c>
-      <c r="E4">
-        <v>-2.174133278395905</v>
-      </c>
-      <c r="F4">
-        <v>2.048193788390227E-25</v>
-      </c>
-      <c r="G4">
+      <c r="D8" s="2">
+        <v>4.3524379596945537E-2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-2.1741332783959049</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2.0481937883902271E-25</v>
+      </c>
+      <c r="G8" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Corrected age</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>0.01277164432737926</v>
-      </c>
-      <c r="D5">
-        <v>0.00100336951974562</v>
-      </c>
-      <c r="E5">
-        <v>0.01274777242151743</v>
-      </c>
-      <c r="F5">
-        <v>0.01713651143117806</v>
-      </c>
-      <c r="G5">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Corrected age</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>0.02698992161029303</v>
-      </c>
-      <c r="D6">
-        <v>0.002187405696485285</v>
-      </c>
-      <c r="E6">
-        <v>0.02693786468408946</v>
-      </c>
-      <c r="F6">
-        <v>0.01972493455119969</v>
-      </c>
-      <c r="G6">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Corrected age</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.05755813706477267</v>
-      </c>
-      <c r="D7">
-        <v>0.004633398857571888</v>
-      </c>
-      <c r="E7">
-        <v>0.05738377037254097</v>
-      </c>
-      <c r="F7">
-        <v>0.0212114270052596</v>
-      </c>
-      <c r="G7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5.7558137064772669E-2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4.633398857571888E-3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5.7383770372540971E-2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2.12114270052596E-2</v>
+      </c>
+      <c r="G9" s="2">
         <v>0.95</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Diversification rates</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>-0.1375512185773598</v>
-      </c>
-      <c r="D8">
-        <v>0.06831350201516094</v>
-      </c>
-      <c r="E8">
-        <v>-0.1350947262761903</v>
-      </c>
-      <c r="F8">
-        <v>0.7551285731178478</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Diversification rates</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.01102855904136375</v>
-      </c>
-      <c r="D9">
-        <v>0.06700746498106026</v>
-      </c>
-      <c r="E9">
-        <v>0.02067446878378114</v>
-      </c>
-      <c r="F9">
-        <v>0.9026086695019916</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Diversification rates</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>0.1578423722075838</v>
-      </c>
-      <c r="D10">
-        <v>0.06550493373567103</v>
-      </c>
-      <c r="E10">
-        <v>0.1680155092445678</v>
-      </c>
-      <c r="F10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.15784237220758379</v>
+      </c>
+      <c r="D10" s="2">
+        <v>6.5504933735671025E-2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.16801550924456779</v>
+      </c>
+      <c r="F10" s="2">
         <v>0.7355873705623428</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>0</v>
       </c>
     </row>
